--- a/data/zh-cn/talents.xlsx
+++ b/data/zh-cn/talents.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiayuankevinguo/Desktop/life-final/data/zh-cn/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65EB08B-1EE1-8948-83AC-41755AAF5C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE4B5CA-1321-694E-8894-133A5966446E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
